--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 07:28</t>
+          <t>更新时间: 2026-07-29 07:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 07:29</t>
+          <t>更新时间: 2026-07-29 07:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 07:31</t>
+          <t>更新时间: 2026-07-29 07:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 07:32</t>
+          <t>更新时间: 2026-07-29 17:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 17:57</t>
+          <t>更新时间: 2026-07-29 18:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 18:16</t>
+          <t>更新时间: 2026-07-29 18:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 18:49</t>
+          <t>更新时间: 2026-07-29 19:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 19:11</t>
+          <t>更新时间: 2026-07-29 19:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 19:50</t>
+          <t>更新时间: 2026-07-30 16:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-30 16:10</t>
+          <t>更新时间: 2026-07-30 17:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-30 17:41</t>
+          <t>更新时间: 2026-07-30 18:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-30 18:03</t>
+          <t>更新时间: 2026-07-30 18:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-30 18:37</t>
+          <t>更新时间: 2026-07-30 19:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-30 19:31</t>
+          <t>更新时间: 2026-07-31 18:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-31 18:05</t>
+          <t>更新时间: 2026-07-31 18:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-31 18:10</t>
+          <t>更新时间: 2026-07-31 19:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-31 19:05</t>
+          <t>更新时间: 2026-07-31 19:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-31 19:34</t>
+          <t>更新时间: 2026-07-31 19:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-31 19:49</t>
+          <t>更新时间: 2026-08-01 16:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-01 16:03</t>
+          <t>更新时间: 2026-08-01 16:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-01 17:35</t>
+          <t>更新时间: 2026-08-01 18:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-01 18:22</t>
+          <t>更新时间: 2026-08-02 16:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-02 16:02</t>
+          <t>更新时间: 2026-08-02 16:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-02 16:58</t>
+          <t>更新时间: 2026-08-02 17:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-02 17:18</t>
+          <t>更新时间: 2026-08-02 17:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-02 17:37</t>
+          <t>更新时间: 2026-08-02 18:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-03 20:42</t>
+          <t>更新时间: 2026-08-03 20:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-03 20:44</t>
+          <t>更新时间: 2026-08-03 21:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-03 21:26</t>
+          <t>更新时间: 2026-08-03 21:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-03 21:48</t>
+          <t>更新时间: 2026-08-04 17:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 17:56</t>
+          <t>更新时间: 2026-08-04 18:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 19:12</t>
+          <t>更新时间: 2026-08-04 19:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 19:50</t>
+          <t>更新时间: 2026-08-05 16:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 16:24</t>
+          <t>更新时间: 2026-08-05 18:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 18:13</t>
+          <t>更新时间: 2026-08-05 18:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 19:45</t>
+          <t>更新时间: 2026-08-06 16:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-06 18:16</t>
+          <t>更新时间: 2026-08-06 18:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-06 19:52</t>
+          <t>更新时间: 2026-08-07 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-07 13:38</t>
+          <t>更新时间: 2026-08-07 13:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-07 13:59</t>
+          <t>更新时间: 2026-08-07 14:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-07 14:18</t>
+          <t>更新时间: 2026-08-07 16:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-08 13:12</t>
+          <t>更新时间: 2026-08-08 14:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-08 14:07</t>
+          <t>更新时间: 2026-08-09 12:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-11 16:13</t>
+          <t>更新时间: 2026-08-12 13:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 13:30</t>
+          <t>更新时间: 2026-08-12 13:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 14:58</t>
+          <t>更新时间: 2026-08-12 16:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 16:49</t>
+          <t>更新时间: 2026-08-13 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-13 13:37</t>
+          <t>更新时间: 2026-08-13 13:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-13 16:52</t>
+          <t>更新时间: 2026-08-14 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 13:31</t>
+          <t>更新时间: 2026-08-14 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 13:01</t>
+          <t>更新时间: 2026-08-16 08:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 13:13</t>
+          <t>更新时间: 2026-08-17 08:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 13:54</t>
+          <t>更新时间: 2026-08-18 08:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 13:16</t>
+          <t>更新时间: 2026-08-19 08:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 08:14</t>
+          <t>更新时间: 2026-08-19 11:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 12:21</t>
+          <t>更新时间: 2026-08-19 13:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 13:17</t>
+          <t>更新时间: 2026-08-20 08:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 12:21</t>
+          <t>更新时间: 2026-08-20 13:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 13:46</t>
+          <t>更新时间: 2026-08-21 08:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 12:23</t>
+          <t>更新时间: 2026-08-21 13:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 13:50</t>
+          <t>更新时间: 2026-08-22 08:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 08:13</t>
+          <t>更新时间: 2026-08-22 11:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 11:10</t>
+          <t>更新时间: 2026-08-22 11:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 11:37</t>
+          <t>更新时间: 2026-08-23 12:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 12:22</t>
+          <t>更新时间: 2026-08-23 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 13:58</t>
+          <t>更新时间: 2026-08-25 08:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 13:49</t>
+          <t>更新时间: 2026-08-26 08:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 08:12</t>
+          <t>更新时间: 2026-08-26 11:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 13:53</t>
+          <t>更新时间: 2026-08-28 14:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 14:24</t>
+          <t>更新时间: 2026-08-28 14:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 05:26</t>
+          <t>更新时间: 2026-08-29 12:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 12:14</t>
+          <t>更新时间: 2026-08-29 15:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 15:00</t>
+          <t>更新时间: 2026-08-29 15:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 15:38</t>
+          <t>更新时间: 2026-08-29 17:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 17:06</t>
+          <t>更新时间: 2026-08-29 18:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 18:56</t>
+          <t>更新时间: 2026-08-30 09:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 09:39</t>
+          <t>更新时间: 2026-08-30 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 13:20</t>
+          <t>更新时间: 2026-08-30 14:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 14:12</t>
+          <t>更新时间: 2026-08-30 16:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 16:21</t>
+          <t>更新时间: 2026-08-30 17:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 17:50</t>
+          <t>更新时间: 2026-08-31 09:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 09:37</t>
+          <t>更新时间: 2026-08-31 13:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 13:28</t>
+          <t>更新时间: 2026-08-31 14:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 14:37</t>
+          <t>更新时间: 2026-08-31 16:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 16:41</t>
+          <t>更新时间: 2026-08-31 18:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 18:41</t>
+          <t>更新时间: 2026-09-01 10:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 10:07</t>
+          <t>更新时间: 2026-09-01 13:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 13:02</t>
+          <t>更新时间: 2026-09-01 13:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 13:59</t>
+          <t>更新时间: 2026-09-01 15:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 15:51</t>
+          <t>更新时间: 2026-09-01 17:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 17:17</t>
+          <t>更新时间: 2026-09-02 09:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 09:22</t>
+          <t>更新时间: 2026-09-02 12:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 12:27</t>
+          <t>更新时间: 2026-09-02 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 13:25</t>
+          <t>更新时间: 2026-09-02 15:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 15:08</t>
+          <t>更新时间: 2026-09-02 16:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 16:37</t>
+          <t>更新时间: 2026-09-03 09:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 09:26</t>
+          <t>更新时间: 2026-09-03 12:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 12:19</t>
+          <t>更新时间: 2026-09-03 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:27</t>
+          <t>更新时间: 2026-09-03 15:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 15:13</t>
+          <t>更新时间: 2026-09-03 16:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 16:45</t>
+          <t>更新时间: 2026-09-04 09:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 09:19</t>
+          <t>更新时间: 2026-09-04 12:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 12:26</t>
+          <t>更新时间: 2026-09-04 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 13:27</t>
+          <t>更新时间: 2026-09-04 15:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 15:16</t>
+          <t>更新时间: 2026-09-04 16:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 16:41</t>
+          <t>更新时间: 2026-09-05 09:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 09:21</t>
+          <t>更新时间: 2026-09-05 12:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 12:21</t>
+          <t>更新时间: 2026-09-05 13:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 13:14</t>
+          <t>更新时间: 2026-09-05 14:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 14:57</t>
+          <t>更新时间: 2026-09-05 16:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 16:13</t>
+          <t>更新时间: 2026-09-06 09:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 09:21</t>
+          <t>更新时间: 2026-09-06 12:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 12:33</t>
+          <t>更新时间: 2026-09-06 13:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:28</t>
+          <t>更新时间: 2026-09-06 15:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 15:09</t>
+          <t>更新时间: 2026-09-06 16:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 16:31</t>
+          <t>更新时间: 2026-09-07 09:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 09:22</t>
+          <t>更新时间: 2026-09-07 12:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 12:33</t>
+          <t>更新时间: 2026-09-07 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 13:38</t>
+          <t>更新时间: 2026-09-07 15:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 15:21</t>
+          <t>更新时间: 2026-09-07 17:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 17:08</t>
+          <t>更新时间: 2026-09-08 09:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 09:30</t>
+          <t>更新时间: 2026-09-08 12:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 12:30</t>
+          <t>更新时间: 2026-09-08 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 13:34</t>
+          <t>更新时间: 2026-09-08 15:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 15:16</t>
+          <t>更新时间: 2026-09-08 16:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 16:44</t>
+          <t>更新时间: 2026-09-09 09:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 09:31</t>
+          <t>更新时间: 2026-09-09 12:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 12:36</t>
+          <t>更新时间: 2026-09-09 13:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 13:41</t>
+          <t>更新时间: 2026-09-09 15:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 15:25</t>
+          <t>更新时间: 2026-09-09 16:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 16:51</t>
+          <t>更新时间: 2026-09-10 09:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 09:29</t>
+          <t>更新时间: 2026-09-10 12:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 12:36</t>
+          <t>更新时间: 2026-09-10 13:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 13:33</t>
+          <t>更新时间: 2026-09-10 15:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 15:21</t>
+          <t>更新时间: 2026-09-10 16:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 16:49</t>
+          <t>更新时间: 2026-09-11 09:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 09:32</t>
+          <t>更新时间: 2026-09-11 12:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 12:34</t>
+          <t>更新时间: 2026-09-11 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 13:36</t>
+          <t>更新时间: 2026-09-11 15:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 15:19</t>
+          <t>更新时间: 2026-09-11 16:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 16:46</t>
+          <t>更新时间: 2026-09-12 09:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 09:30</t>
+          <t>更新时间: 2026-09-12 12:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 12:30</t>
+          <t>更新时间: 2026-09-12 13:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 13:22</t>
+          <t>更新时间: 2026-09-12 15:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 15:11</t>
+          <t>更新时间: 2026-09-12 16:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 16:31</t>
+          <t>更新时间: 2026-09-13 09:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 09:26</t>
+          <t>更新时间: 2026-09-13 12:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 12:41</t>
+          <t>更新时间: 2026-09-13 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 13:38</t>
+          <t>更新时间: 2026-09-13 15:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 15:30</t>
+          <t>更新时间: 2026-09-13 17:19</t>
         </is>
       </c>
     </row>
